--- a/test/fixtures/files/Sara-Alert-Format-Invalid-Fields.xlsx
+++ b/test/fixtures/files/Sara-Alert-Format-Invalid-Fields.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/twong/Documents/SARA-ALERT/SaraAlert/test/fixtures/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB9CFCE-9727-2740-AC2C-C3165576776F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14D5792-C6AE-5B46-AEF4-B3679A1406FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="33600" windowHeight="19380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="257">
   <si>
     <t>First Name</t>
   </si>
@@ -782,6 +782,15 @@
   </si>
   <si>
     <t>32ntkgmavd</t>
+  </si>
+  <si>
+    <t>Follow-Up Reason</t>
+  </si>
+  <si>
+    <t>Follow-Up Note</t>
+  </si>
+  <si>
+    <t>invalid reason</t>
   </si>
 </sst>
 </file>
@@ -1134,7 +1143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DH12"/>
+  <dimension ref="A1:DJ12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
@@ -1248,9 +1257,11 @@
     <col min="110" max="110" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="111" max="111" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="112" max="112" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1587,8 +1598,14 @@
       <c r="DH1" t="s">
         <v>237</v>
       </c>
+      <c r="DI1" t="s">
+        <v>254</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>255</v>
+      </c>
     </row>
-    <row r="2" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:114" x14ac:dyDescent="0.15">
       <c r="D2" s="1" t="s">
         <v>219</v>
       </c>
@@ -1824,8 +1841,11 @@
       <c r="DH2" t="s">
         <v>251</v>
       </c>
+      <c r="DI2" t="s">
+        <v>256</v>
+      </c>
     </row>
-    <row r="3" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:114" x14ac:dyDescent="0.15">
       <c r="D3" s="1" t="s">
         <v>220</v>
       </c>
@@ -1867,7 +1887,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="4" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>165</v>
       </c>
@@ -2106,7 +2126,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="5" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>94</v>
       </c>
@@ -2369,13 +2389,13 @@
         <v>164</v>
       </c>
     </row>
-    <row r="6" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:114" x14ac:dyDescent="0.15">
       <c r="BT6" s="1"/>
       <c r="BU6" s="1"/>
       <c r="BW6" s="1"/>
       <c r="CB6" s="1"/>
     </row>
-    <row r="7" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:114" x14ac:dyDescent="0.15">
       <c r="D7" s="2"/>
       <c r="BL7" s="2"/>
       <c r="BM7" s="2"/>
@@ -2388,7 +2408,7 @@
       <c r="CO7" s="2"/>
       <c r="CP7" s="3"/>
     </row>
-    <row r="8" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:114" x14ac:dyDescent="0.15">
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -2405,7 +2425,7 @@
       <c r="CB8" s="1"/>
       <c r="CD8" s="1"/>
     </row>
-    <row r="9" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:114" x14ac:dyDescent="0.15">
       <c r="D9" s="3"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -2422,7 +2442,7 @@
       <c r="CC9" s="1"/>
       <c r="CD9" s="1"/>
     </row>
-    <row r="10" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:114" x14ac:dyDescent="0.15">
       <c r="AZ10" s="2"/>
       <c r="BE10" s="2"/>
       <c r="BO10" s="3"/>
@@ -2431,7 +2451,7 @@
       <c r="CO10" s="3"/>
       <c r="CP10" s="2"/>
     </row>
-    <row r="12" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:114" x14ac:dyDescent="0.15">
       <c r="D12" s="1"/>
     </row>
   </sheetData>

--- a/test/fixtures/files/Sara-Alert-Format-Invalid-Fields.xlsx
+++ b/test/fixtures/files/Sara-Alert-Format-Invalid-Fields.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/twong/Documents/SARA-ALERT/SaraAlert/test/fixtures/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14D5792-C6AE-5B46-AEF4-B3679A1406FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF5F0C4-F69B-444E-B462-29C1158648B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="33600" windowHeight="19380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="258">
   <si>
     <t>First Name</t>
   </si>
@@ -791,6 +791,9 @@
   </si>
   <si>
     <t>invalid reason</t>
+  </si>
+  <si>
+    <t>note</t>
   </si>
 </sst>
 </file>
@@ -1886,6 +1889,9 @@
       <c r="DH3" t="s">
         <v>252</v>
       </c>
+      <c r="DJ3" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="4" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A4" t="s">

--- a/test/fixtures/files/Sara-Alert-Format-Invalid-Fields.xlsx
+++ b/test/fixtures/files/Sara-Alert-Format-Invalid-Fields.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/twong/Documents/SARA-ALERT/SaraAlert/test/fixtures/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB9CFCE-9727-2740-AC2C-C3165576776F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF5F0C4-F69B-444E-B462-29C1158648B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="33600" windowHeight="19380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="258">
   <si>
     <t>First Name</t>
   </si>
@@ -782,6 +782,18 @@
   </si>
   <si>
     <t>32ntkgmavd</t>
+  </si>
+  <si>
+    <t>Follow-Up Reason</t>
+  </si>
+  <si>
+    <t>Follow-Up Note</t>
+  </si>
+  <si>
+    <t>invalid reason</t>
+  </si>
+  <si>
+    <t>note</t>
   </si>
 </sst>
 </file>
@@ -1134,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DH12"/>
+  <dimension ref="A1:DJ12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
@@ -1248,9 +1260,11 @@
     <col min="110" max="110" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="111" max="111" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="112" max="112" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1587,8 +1601,14 @@
       <c r="DH1" t="s">
         <v>237</v>
       </c>
+      <c r="DI1" t="s">
+        <v>254</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>255</v>
+      </c>
     </row>
-    <row r="2" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:114" x14ac:dyDescent="0.15">
       <c r="D2" s="1" t="s">
         <v>219</v>
       </c>
@@ -1824,8 +1844,11 @@
       <c r="DH2" t="s">
         <v>251</v>
       </c>
+      <c r="DI2" t="s">
+        <v>256</v>
+      </c>
     </row>
-    <row r="3" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:114" x14ac:dyDescent="0.15">
       <c r="D3" s="1" t="s">
         <v>220</v>
       </c>
@@ -1866,8 +1889,11 @@
       <c r="DH3" t="s">
         <v>252</v>
       </c>
+      <c r="DJ3" t="s">
+        <v>257</v>
+      </c>
     </row>
-    <row r="4" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>165</v>
       </c>
@@ -2106,7 +2132,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="5" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>94</v>
       </c>
@@ -2369,13 +2395,13 @@
         <v>164</v>
       </c>
     </row>
-    <row r="6" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:114" x14ac:dyDescent="0.15">
       <c r="BT6" s="1"/>
       <c r="BU6" s="1"/>
       <c r="BW6" s="1"/>
       <c r="CB6" s="1"/>
     </row>
-    <row r="7" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:114" x14ac:dyDescent="0.15">
       <c r="D7" s="2"/>
       <c r="BL7" s="2"/>
       <c r="BM7" s="2"/>
@@ -2388,7 +2414,7 @@
       <c r="CO7" s="2"/>
       <c r="CP7" s="3"/>
     </row>
-    <row r="8" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:114" x14ac:dyDescent="0.15">
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -2405,7 +2431,7 @@
       <c r="CB8" s="1"/>
       <c r="CD8" s="1"/>
     </row>
-    <row r="9" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:114" x14ac:dyDescent="0.15">
       <c r="D9" s="3"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -2422,7 +2448,7 @@
       <c r="CC9" s="1"/>
       <c r="CD9" s="1"/>
     </row>
-    <row r="10" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:114" x14ac:dyDescent="0.15">
       <c r="AZ10" s="2"/>
       <c r="BE10" s="2"/>
       <c r="BO10" s="3"/>
@@ -2431,7 +2457,7 @@
       <c r="CO10" s="3"/>
       <c r="CP10" s="2"/>
     </row>
-    <row r="12" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:114" x14ac:dyDescent="0.15">
       <c r="D12" s="1"/>
     </row>
   </sheetData>
